--- a/data/analysis/supervision_profiles.xlsx
+++ b/data/analysis/supervision_profiles.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1089,12 +1089,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10_MUHAMMAD_EHATISHAM</t>
+          <t>09_SANA_FATIMA_RIZVI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Muhammad Ehatisham</t>
+          <t>Sana Fatima Rizvi</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 10_MUHAMMAD_EHATISHAM. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 09_SANA_FATIMA_RIZVI. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1153,12 +1153,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11_WAQAS_AMIN</t>
+          <t>10_MUHAMMAD_EHATISHAM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Waqas Amin</t>
+          <t>Muhammad Ehatisham</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 11_WAQAS_AMIN. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 10_MUHAMMAD_EHATISHAM. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1217,12 +1217,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12_SYED_TAMOORULHASSAN</t>
+          <t>11_WAQAS_AMIN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SYED TAMOORULHASSAN</t>
+          <t>Waqas Amin</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 12_SYED_TAMOORULHASSAN. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 11_WAQAS_AMIN. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1281,12 +1281,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13_MANZOOR_ELLAHI</t>
+          <t>12_SYED_TAMOORULHASSAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Manzoor Ellahi</t>
+          <t>SYED TAMOORULHASSAN</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 13_MANZOOR_ELLAHI. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 12_SYED_TAMOORULHASSAN. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1345,12 +1345,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14_SAROSH_TAHIR</t>
+          <t>13_MANZOOR_ELLAHI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sarosh Tahir</t>
+          <t>Manzoor Ellahi</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 14_SAROSH_TAHIR. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 13_MANZOOR_ELLAHI. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1409,12 +1409,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>15_M_USMAN_ABBASI</t>
+          <t>14_SAROSH_TAHIR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M. Usman Abbasi</t>
+          <t>Sarosh Tahir</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 15_M_USMAN_ABBASI. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 14_SAROSH_TAHIR. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1473,12 +1473,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16_MUZZAMIL_GHAFFAR</t>
+          <t>15_M_USMAN_ABBASI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Muzzamil Ghaffar</t>
+          <t>M. Usman Abbasi</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 16_MUZZAMIL_GHAFFAR. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 15_M_USMAN_ABBASI. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1537,12 +1537,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17_SUHAIL_ASGHAR</t>
+          <t>16_MUZZAMIL_GHAFFAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Suhail Asghar Qureshi</t>
+          <t>Muzzamil Ghaffar</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 17_SUHAIL_ASGHAR. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 16_MUZZAMIL_GHAFFAR. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1601,12 +1601,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18_MUHAMMAD_AMJAD</t>
+          <t>17_SUHAIL_ASGHAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Muhammad Amjad</t>
+          <t>Suhail Asghar Qureshi</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 18_MUHAMMAD_AMJAD. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 17_SUHAIL_ASGHAR. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1665,12 +1665,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19_ASIM_MASOOD</t>
+          <t>18_MUHAMMAD_AMJAD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Asim Masood</t>
+          <t>Muhammad Amjad</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 19_ASIM_MASOOD. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 18_MUHAMMAD_AMJAD. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1729,12 +1729,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20_SYED_FASIH_ALI</t>
+          <t>19_ASIM_MASOOD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Syed Fasih Ali</t>
+          <t>Asim Masood</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 20_SYED_FASIH_ALI. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 19_ASIM_MASOOD. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1793,12 +1793,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21_SAMAN_FATIMA</t>
+          <t>20_SYED_FASIH_ALI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Saman Fatima</t>
+          <t>Syed Fasih Ali</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 21_SAMAN_FATIMA. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 20_SYED_FASIH_ALI. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1857,12 +1857,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>22_ZEESHAN</t>
+          <t>21_SAMAN_FATIMA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zeeshan</t>
+          <t>Saman Fatima</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 22_ZEESHAN. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 21_SAMAN_FATIMA. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1921,12 +1921,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>23_WAQAS_TARIQ_TOOR</t>
+          <t>22_ZEESHAN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Waqas Tariq Toor</t>
+          <t>Zeeshan</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 23_WAQAS_TARIQ_TOOR. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 22_ZEESHAN. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -1985,12 +1985,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>24_AHMED_NAEEM</t>
+          <t>23_WAQAS_TARIQ_TOOR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ahmed Naeem</t>
+          <t>Waqas Tariq Toor</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 24_AHMED_NAEEM. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 23_WAQAS_TARIQ_TOOR. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
+          <t>24_AHMED_NAEEM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MUHAMMAD ADEEL ALTAF</t>
+          <t>Ahmed Naeem</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 25_MUHAMMAD_ADEEL_ALTAF. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 24_AHMED_NAEEM. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2113,12 +2113,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26_AAMINA_AKBAR</t>
+          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aamina Akbar</t>
+          <t>MUHAMMAD ADEEL ALTAF</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 26_AAMINA_AKBAR. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 25_MUHAMMAD_ADEEL_ALTAF. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2177,12 +2177,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27_SHAHEER</t>
+          <t>26_AAMINA_AKBAR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shaheer</t>
+          <t>Aamina Akbar</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 27_SHAHEER. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 26_AAMINA_AKBAR. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2241,12 +2241,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>28_IDRIS_KHAN</t>
+          <t>27_SHAHEER</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Idris Khan</t>
+          <t>Shaheer</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 28_IDRIS_KHAN. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 27_SHAHEER. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2305,12 +2305,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>29_MUHAMMAD_SARMAD_TARIQ</t>
+          <t>28_IDRIS_KHAN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Muhammad Sarmad Tariq</t>
+          <t>Idris Khan</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 29_MUHAMMAD_SARMAD_TARIQ. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 28_IDRIS_KHAN. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2369,12 +2369,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>30_FAHD_SIKANDAR_KHAN</t>
+          <t>29_MUHAMMAD_SARMAD_TARIQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fahd Sikandar Khan</t>
+          <t>Muhammad Sarmad Tariq</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 30_FAHD_SIKANDAR_KHAN. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 29_MUHAMMAD_SARMAD_TARIQ. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2433,12 +2433,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>31_USMAN_MASUD</t>
+          <t>30_FAHD_SIKANDAR_KHAN</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Usman Masud</t>
+          <t>Fahd Sikandar Khan</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 31_USMAN_MASUD. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 30_FAHD_SIKANDAR_KHAN. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2497,12 +2497,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>32_QAISAR_HUSSAIN_ALVI</t>
+          <t>31_USMAN_MASUD</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Qaisar Hussain Alvi</t>
+          <t>Usman Masud</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 32_QAISAR_HUSSAIN_ALVI. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 31_USMAN_MASUD. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2561,12 +2561,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>33_QAMAR_ABBAS</t>
+          <t>32_QAISAR_HUSSAIN_ALVI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Qamar Abbas</t>
+          <t>Qaisar Hussain Alvi</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 33_QAMAR_ABBAS. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 32_QAISAR_HUSSAIN_ALVI. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2625,12 +2625,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>34_SHAHZAD</t>
+          <t>33_QAMAR_ABBAS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shahzad</t>
+          <t>Qamar Abbas</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 34_SHAHZAD. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 33_QAMAR_ABBAS. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2689,12 +2689,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>35_MATIULLAH_AHSAN</t>
+          <t>34_SHAHZAD</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Matiullah Ahsan</t>
+          <t>Shahzad</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 35_MATIULLAH_AHSAN. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 34_SHAHZAD. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2753,12 +2753,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>36_SAMANA_BATOOL</t>
+          <t>35_MATIULLAH_AHSAN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Samana Batool</t>
+          <t>Matiullah Ahsan</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 36_SAMANA_BATOOL. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 35_MATIULLAH_AHSAN. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2817,12 +2817,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>37_SANIA_GUL</t>
+          <t>36_SAMANA_BATOOL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sania Gul</t>
+          <t>Samana Batool</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 37_SANIA_GUL. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 36_SAMANA_BATOOL. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -2881,12 +2881,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>38_MUHAMMAD_MUSADIQ</t>
+          <t>37_SANIA_GUL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Muhammad Musadiq Ahmed</t>
+          <t>Sania Gul</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 38_MUHAMMAD_MUSADIQ. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 37_SANIA_GUL. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -2945,12 +2945,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>39_MUHAMMAD_SAQIB</t>
+          <t>38_MUHAMMAD_MUSADIQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Muhammad Saqib</t>
+          <t>Muhammad Musadiq Ahmed</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 39_MUHAMMAD_SAQIB. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 38_MUHAMMAD_MUSADIQ. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3009,12 +3009,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>40_ABDUR_REHMAN</t>
+          <t>39_MUHAMMAD_SAQIB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Abdur Rehman</t>
+          <t>Muhammad Saqib</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 40_ABDUR_REHMAN. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 39_MUHAMMAD_SAQIB. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3073,12 +3073,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>41_MUHAMMAD_AQEEL</t>
+          <t>40_ABDUR_REHMAN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Muhammad Aqeel</t>
+          <t>Abdur Rehman</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 41_MUHAMMAD_AQEEL. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 40_ABDUR_REHMAN. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3137,12 +3137,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>42_SAQIB_JAMIL</t>
+          <t>41_MUHAMMAD_AQEEL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Saqib Jamil</t>
+          <t>Muhammad Aqeel</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>No supervision information was found in the CV of 42_SAQIB_JAMIL. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+          <t>No supervision information was found in the CV of 41_MUHAMMAD_AQEEL. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3201,62 +3201,190 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>42_SAQIB_JAMIL</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Saqib Jamil</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Needs Clarification</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>No supervision information was found in the CV of 42_SAQIB_JAMIL. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Needs Clarification</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>REQUEST_SUPERVISION_DATA</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>43_AMMARA_NASIM</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Ammara Nasim</t>
         </is>
       </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L44" t="b">
-        <v>1</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Needs Clarification</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L45" t="b">
+        <v>1</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Needs Clarification</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>No supervision information was found in the CV of 43_AMMARA_NASIM. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Needs Clarification</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Needs Clarification</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>REQUEST_SUPERVISION_DATA</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Muhammad_Dawood_Rizwan_CV</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L46" t="b">
+        <v>1</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Needs Clarification</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>No supervision information was found in the CV of Muhammad_Dawood_Rizwan_CV. This candidate has been flagged for follow-up to provide details of supervised MS/PhD students including names, degree levels, and graduation years.</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Needs Clarification</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>REQUEST_SUPERVISION_DATA</t>
         </is>
